--- a/QR-Generator-mail-sender/email.xlsx
+++ b/QR-Generator-mail-sender/email.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t xml:space="preserve">Team Name </t>
   </si>
@@ -35,30 +35,6 @@
   </si>
   <si>
     <t xml:space="preserve">Email ID(team member)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anshu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24BCE11527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANSHU.24BCE11527@VITBHOPAL.AC.IN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANSHU.24BSA10030@VITBHOPAL.AC.IN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sumit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24BCE11520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUMIT.24BCE11520@VITBHOPAL.AC.IN</t>
   </si>
 </sst>
 </file>
@@ -73,6 +49,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -93,12 +70,14 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -143,20 +122,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -286,83 +269,47 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34.97"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>12</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="ANSHU.24BCE11527@VITBHOPAL.AC.IN"/>
-    <hyperlink ref="E2" r:id="rId2" display="ANSHU.24BCE11527@VITBHOPAL.AC.IN"/>
-    <hyperlink ref="D3" r:id="rId3" display="ANSHU.24BCE11527@VITBHOPAL.AC.IN"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
